--- a/artfynd/A 29945-2022 artfynd.xlsx
+++ b/artfynd/A 29945-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29945-2022 artfynd.xlsx
+++ b/artfynd/A 29945-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105311952</v>
+        <v>113678015</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457717.9085133106</v>
+        <v>457373</v>
       </c>
       <c r="R2" t="n">
-        <v>7151475.293391743</v>
+        <v>7151572</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,18 +758,9 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -790,22 +770,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111011864</v>
+        <v>113678019</v>
       </c>
       <c r="B3" t="n">
-        <v>85715</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,26 +792,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457566.1286299905</v>
+        <v>457730</v>
       </c>
       <c r="R3" t="n">
-        <v>7151552.436993674</v>
+        <v>7151536</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,27 +871,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111011899</v>
+        <v>113678020</v>
       </c>
       <c r="B4" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,26 +898,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457578.2940309282</v>
+        <v>457743</v>
       </c>
       <c r="R4" t="n">
-        <v>7151526.824662624</v>
+        <v>7151536</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,66 +977,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112328247</v>
+        <v>113680333</v>
       </c>
       <c r="B5" t="n">
-        <v>77850</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457353</v>
+        <v>457816</v>
       </c>
       <c r="R5" t="n">
-        <v>7151591</v>
+        <v>7151485</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,21 +1061,11 @@
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1128,9 +1076,14 @@
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1138,14 +1091,18 @@
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680329</v>
+        <v>113679106</v>
       </c>
       <c r="B6" t="n">
-        <v>91916</v>
+        <v>83350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457630</v>
+        <v>457586</v>
       </c>
       <c r="R6" t="n">
-        <v>7151512</v>
+        <v>7151563</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,12 +1181,12 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW6" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1248,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680342</v>
+        <v>113679121</v>
       </c>
       <c r="B7" t="n">
-        <v>83180</v>
+        <v>83350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457850</v>
+        <v>457680</v>
       </c>
       <c r="R7" t="n">
-        <v>7151597</v>
+        <v>7151576</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,12 +1287,12 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW7" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1354,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113679140</v>
+        <v>113679129</v>
       </c>
       <c r="B8" t="n">
-        <v>83314</v>
+        <v>83350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457820</v>
+        <v>457742</v>
       </c>
       <c r="R8" t="n">
-        <v>7151598</v>
+        <v>7151530</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,48 +1417,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113679102</v>
+        <v>111011864</v>
       </c>
       <c r="B9" t="n">
-        <v>80466</v>
+        <v>89292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457437</v>
+        <v>457566</v>
       </c>
       <c r="R9" t="n">
-        <v>7151514</v>
+        <v>7151553</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,12 +1485,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,59 +1499,51 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113680326</v>
+        <v>113680328</v>
       </c>
       <c r="B10" t="n">
-        <v>91879</v>
+        <v>89354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457522</v>
+        <v>457572</v>
       </c>
       <c r="R10" t="n">
-        <v>7151575</v>
+        <v>7151580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113679135</v>
+        <v>113680336</v>
       </c>
       <c r="B11" t="n">
-        <v>83314</v>
+        <v>92245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,21 +1635,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1707,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457883</v>
+        <v>457836</v>
       </c>
       <c r="R11" t="n">
-        <v>7151595</v>
+        <v>7151512</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1754,12 +1706,12 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW11" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1778,32 +1730,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113679117</v>
+        <v>105315253</v>
       </c>
       <c r="B12" t="n">
-        <v>80466</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,13 +1765,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457678</v>
+        <v>457967</v>
       </c>
       <c r="R12" t="n">
-        <v>7151491</v>
+        <v>7151502</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,12 +1795,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1814,7 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Susanne Wiik</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1873,21 +1825,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680339</v>
+        <v>113680327</v>
       </c>
       <c r="B13" t="n">
-        <v>91930</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1919,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457876</v>
+        <v>457538</v>
       </c>
       <c r="R13" t="n">
-        <v>7151601</v>
+        <v>7151581</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,32 +1938,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113679128</v>
+        <v>113680329</v>
       </c>
       <c r="B14" t="n">
-        <v>83297</v>
+        <v>91974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2025,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457745</v>
+        <v>457630</v>
       </c>
       <c r="R14" t="n">
-        <v>7151531</v>
+        <v>7151512</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2072,12 +2020,12 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW14" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2096,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113679104</v>
+        <v>113680334</v>
       </c>
       <c r="B15" t="n">
-        <v>83314</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,34 +2055,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457453</v>
+        <v>457842</v>
       </c>
       <c r="R15" t="n">
-        <v>7151510</v>
+        <v>7151516</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,12 +2126,12 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW15" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2202,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113679088</v>
+        <v>113680338</v>
       </c>
       <c r="B16" t="n">
-        <v>80437</v>
+        <v>91974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,34 +2161,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457335</v>
+        <v>457864</v>
       </c>
       <c r="R16" t="n">
-        <v>7151600</v>
+        <v>7151544</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,12 +2232,12 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW16" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2308,32 +2256,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113679123</v>
+        <v>113680318</v>
       </c>
       <c r="B17" t="n">
-        <v>79588</v>
+        <v>91988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6459</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2343,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457694</v>
+        <v>457551</v>
       </c>
       <c r="R17" t="n">
-        <v>7151523</v>
+        <v>7151637</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,12 +2338,12 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW17" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2414,32 +2362,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113679132</v>
+        <v>113680339</v>
       </c>
       <c r="B18" t="n">
-        <v>80473</v>
+        <v>91988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2449,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457805</v>
+        <v>457876</v>
       </c>
       <c r="R18" t="n">
-        <v>7151514</v>
+        <v>7151601</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2496,12 +2444,12 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW18" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2520,48 +2468,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113679121</v>
+        <v>112328247</v>
       </c>
       <c r="B19" t="n">
-        <v>83306</v>
+        <v>79486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>1249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457680</v>
+        <v>457354</v>
       </c>
       <c r="R19" t="n">
-        <v>7151576</v>
+        <v>7151591</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,11 +2537,21 @@
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-09-26</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2601,16 +2560,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -2618,40 +2572,36 @@
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113679084</v>
+        <v>113679137</v>
       </c>
       <c r="B20" t="n">
-        <v>83319</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2661,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457591</v>
+        <v>457878</v>
       </c>
       <c r="R20" t="n">
-        <v>7151669</v>
+        <v>7151593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,10 +2682,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113679100</v>
+        <v>113680319</v>
       </c>
       <c r="B21" t="n">
-        <v>80438</v>
+        <v>83222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,21 +2693,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2767,10 +2717,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457436</v>
+        <v>457396</v>
       </c>
       <c r="R21" t="n">
-        <v>7151513</v>
+        <v>7151641</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,12 +2764,12 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW21" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -2838,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113680319</v>
+        <v>113680321</v>
       </c>
       <c r="B22" t="n">
-        <v>83180</v>
+        <v>83222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2873,10 +2823,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457396</v>
+        <v>457378</v>
       </c>
       <c r="R22" t="n">
-        <v>7151641</v>
+        <v>7151652</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2944,32 +2894,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113679110</v>
+        <v>113680330</v>
       </c>
       <c r="B23" t="n">
-        <v>79588</v>
+        <v>83222</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6459</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2979,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457606</v>
+        <v>457701</v>
       </c>
       <c r="R23" t="n">
-        <v>7151530</v>
+        <v>7151487</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,12 +2976,12 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW23" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3050,10 +3000,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113679108</v>
+        <v>113680337</v>
       </c>
       <c r="B24" t="n">
-        <v>80438</v>
+        <v>83222</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3061,21 +3011,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3085,10 +3035,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457606</v>
+        <v>457840</v>
       </c>
       <c r="R24" t="n">
-        <v>7151532</v>
+        <v>7151527</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3132,12 +3082,12 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW24" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3156,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113679091</v>
+        <v>113680342</v>
       </c>
       <c r="B25" t="n">
-        <v>80438</v>
+        <v>83222</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,34 +3117,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457365</v>
+        <v>457850</v>
       </c>
       <c r="R25" t="n">
-        <v>7151603</v>
+        <v>7151597</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3238,12 +3188,12 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW25" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3262,10 +3212,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113679086</v>
+        <v>113680343</v>
       </c>
       <c r="B26" t="n">
-        <v>83314</v>
+        <v>83222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,34 +3223,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457366</v>
+        <v>457803</v>
       </c>
       <c r="R26" t="n">
-        <v>7151654</v>
+        <v>7151599</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3344,12 +3294,12 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW26" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3368,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113679139</v>
+        <v>113680346</v>
       </c>
       <c r="B27" t="n">
-        <v>83314</v>
+        <v>83222</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3379,21 +3329,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3403,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457848</v>
+        <v>457802</v>
       </c>
       <c r="R27" t="n">
-        <v>7151605</v>
+        <v>7151613</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3450,12 +3400,12 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW27" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3474,45 +3424,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113679094</v>
+        <v>113679084</v>
       </c>
       <c r="B28" t="n">
-        <v>80472</v>
+        <v>83363</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>1467</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457381</v>
+        <v>457591</v>
       </c>
       <c r="R28" t="n">
-        <v>7151579</v>
+        <v>7151669</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3580,10 +3530,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113679099</v>
+        <v>111011899</v>
       </c>
       <c r="B29" t="n">
-        <v>80437</v>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3591,37 +3541,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457437</v>
+        <v>457578</v>
       </c>
       <c r="R29" t="n">
-        <v>7151513</v>
+        <v>7151527</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3645,12 +3598,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3659,37 +3612,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113680320</v>
+        <v>113679091</v>
       </c>
       <c r="B30" t="n">
-        <v>91936</v>
+        <v>80489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3697,19 +3642,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3717,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457385</v>
+        <v>457365</v>
       </c>
       <c r="R30" t="n">
-        <v>7151640</v>
+        <v>7151603</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3764,12 +3713,12 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW30" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3788,45 +3737,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113680317</v>
+        <v>113679095</v>
       </c>
       <c r="B31" t="n">
-        <v>91879</v>
+        <v>80489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457556</v>
+        <v>457383</v>
       </c>
       <c r="R31" t="n">
-        <v>7151639</v>
+        <v>7151579</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,12 +3819,12 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW31" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -3894,10 +3843,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113679095</v>
+        <v>113679100</v>
       </c>
       <c r="B32" t="n">
-        <v>80438</v>
+        <v>80489</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3929,10 +3878,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457383</v>
+        <v>457436</v>
       </c>
       <c r="R32" t="n">
-        <v>7151579</v>
+        <v>7151513</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4000,10 +3949,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113679087</v>
+        <v>113679108</v>
       </c>
       <c r="B33" t="n">
-        <v>80437</v>
+        <v>80489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4011,34 +3960,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457332</v>
+        <v>457606</v>
       </c>
       <c r="R33" t="n">
-        <v>7151642</v>
+        <v>7151532</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,10 +4055,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113679124</v>
+        <v>113679119</v>
       </c>
       <c r="B34" t="n">
-        <v>80437</v>
+        <v>80489</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4117,21 +4066,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4141,10 +4090,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457706</v>
+        <v>457686</v>
       </c>
       <c r="R34" t="n">
-        <v>7151522</v>
+        <v>7151510</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4212,45 +4161,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113679103</v>
+        <v>113679122</v>
       </c>
       <c r="B35" t="n">
-        <v>80473</v>
+        <v>80489</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>457439</v>
+        <v>457692</v>
       </c>
       <c r="R35" t="n">
-        <v>7151514</v>
+        <v>7151526</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4318,45 +4267,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113679096</v>
+        <v>113678014</v>
       </c>
       <c r="B36" t="n">
-        <v>80437</v>
+        <v>96413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457373</v>
+        <v>457372</v>
       </c>
       <c r="R36" t="n">
-        <v>7151548</v>
+        <v>7151602</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4397,13 +4350,9 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4424,10 +4373,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113680345</v>
+        <v>113678016</v>
       </c>
       <c r="B37" t="n">
-        <v>91879</v>
+        <v>96413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4435,34 +4384,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457799</v>
+        <v>457465</v>
       </c>
       <c r="R37" t="n">
-        <v>7151616</v>
+        <v>7151542</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4503,15 +4456,11 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW37" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -4530,45 +4479,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113680321</v>
+        <v>113678017</v>
       </c>
       <c r="B38" t="n">
-        <v>83180</v>
+        <v>96413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457378</v>
+        <v>457707</v>
       </c>
       <c r="R38" t="n">
-        <v>7151652</v>
+        <v>7151539</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4609,15 +4562,11 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW38" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -4636,45 +4585,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113680336</v>
+        <v>113678021</v>
       </c>
       <c r="B39" t="n">
-        <v>92215</v>
+        <v>96413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457836</v>
+        <v>457872</v>
       </c>
       <c r="R39" t="n">
-        <v>7151512</v>
+        <v>7151605</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4715,15 +4668,11 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW39" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -4742,10 +4691,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113679126</v>
+        <v>113678018</v>
       </c>
       <c r="B40" t="n">
-        <v>80473</v>
+        <v>96425</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4753,34 +4702,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>2813</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457698</v>
+        <v>457732</v>
       </c>
       <c r="R40" t="n">
-        <v>7151521</v>
+        <v>7151541</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,13 +4774,9 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AS40" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4848,32 +4797,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113679119</v>
+        <v>113680335</v>
       </c>
       <c r="B41" t="n">
-        <v>80438</v>
+        <v>92199</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4832,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457686</v>
+        <v>457831</v>
       </c>
       <c r="R41" t="n">
-        <v>7151510</v>
+        <v>7151507</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4930,12 +4879,12 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW41" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -4954,10 +4903,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113680341</v>
+        <v>113680324</v>
       </c>
       <c r="B42" t="n">
-        <v>91879</v>
+        <v>92943</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,34 +4914,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457867</v>
+        <v>457400</v>
       </c>
       <c r="R42" t="n">
-        <v>7151616</v>
+        <v>7151519</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5060,32 +5009,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113679142</v>
+        <v>113680317</v>
       </c>
       <c r="B43" t="n">
-        <v>79332</v>
+        <v>91937</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5095,10 +5044,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457794</v>
+        <v>457556</v>
       </c>
       <c r="R43" t="n">
-        <v>7151623</v>
+        <v>7151639</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5142,12 +5091,12 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW43" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -5166,10 +5115,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113679116</v>
+        <v>113680322</v>
       </c>
       <c r="B44" t="n">
-        <v>80472</v>
+        <v>91937</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5177,34 +5126,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457677</v>
+        <v>457373</v>
       </c>
       <c r="R44" t="n">
-        <v>7151501</v>
+        <v>7151657</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5248,12 +5197,12 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AS44" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW44" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -5272,10 +5221,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113679092</v>
+        <v>113680325</v>
       </c>
       <c r="B45" t="n">
-        <v>80466</v>
+        <v>91937</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5283,21 +5232,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5307,10 +5256,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457382</v>
+        <v>457456</v>
       </c>
       <c r="R45" t="n">
-        <v>7151577</v>
+        <v>7151513</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5354,12 +5303,12 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AS45" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW45" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -5378,10 +5327,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113679118</v>
+        <v>113680326</v>
       </c>
       <c r="B46" t="n">
-        <v>80472</v>
+        <v>91937</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5389,21 +5338,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5413,10 +5362,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457687</v>
+        <v>457522</v>
       </c>
       <c r="R46" t="n">
-        <v>7151509</v>
+        <v>7151575</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5460,12 +5409,12 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW46" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -5484,10 +5433,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113680325</v>
+        <v>113680331</v>
       </c>
       <c r="B47" t="n">
-        <v>91879</v>
+        <v>91937</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5515,14 +5464,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457456</v>
+        <v>457728</v>
       </c>
       <c r="R47" t="n">
-        <v>7151513</v>
+        <v>7151521</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5590,10 +5539,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113679098</v>
+        <v>113680340</v>
       </c>
       <c r="B48" t="n">
-        <v>80397</v>
+        <v>91937</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5601,34 +5550,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457435</v>
+        <v>457871</v>
       </c>
       <c r="R48" t="n">
-        <v>7151509</v>
+        <v>7151603</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5672,12 +5621,12 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW48" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -5696,32 +5645,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113680328</v>
+        <v>113680341</v>
       </c>
       <c r="B49" t="n">
-        <v>89299</v>
+        <v>91937</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5731,10 +5680,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457572</v>
+        <v>457867</v>
       </c>
       <c r="R49" t="n">
-        <v>7151580</v>
+        <v>7151616</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5802,41 +5751,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113680323</v>
+        <v>113680344</v>
       </c>
       <c r="B50" t="n">
-        <v>91936</v>
+        <v>91937</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457372</v>
+        <v>457785</v>
       </c>
       <c r="R50" t="n">
-        <v>7151656</v>
+        <v>7151608</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,32 +5857,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113680333</v>
+        <v>113680345</v>
       </c>
       <c r="B51" t="n">
-        <v>91866</v>
+        <v>91937</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5939,10 +5892,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457816</v>
+        <v>457799</v>
       </c>
       <c r="R51" t="n">
-        <v>7151485</v>
+        <v>7151616</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6010,32 +5963,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113679085</v>
+        <v>113679142</v>
       </c>
       <c r="B52" t="n">
-        <v>83314</v>
+        <v>79373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6045,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457529</v>
+        <v>457794</v>
       </c>
       <c r="R52" t="n">
-        <v>7151643</v>
+        <v>7151623</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6116,32 +6069,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113680330</v>
+        <v>113679120</v>
       </c>
       <c r="B53" t="n">
-        <v>83180</v>
+        <v>83341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6151,10 +6104,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457701</v>
+        <v>457679</v>
       </c>
       <c r="R53" t="n">
-        <v>7151487</v>
+        <v>7151537</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6198,12 +6151,12 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW53" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -6222,45 +6175,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113679097</v>
+        <v>113679128</v>
       </c>
       <c r="B54" t="n">
-        <v>80437</v>
+        <v>83341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457413</v>
+        <v>457745</v>
       </c>
       <c r="R54" t="n">
-        <v>7151504</v>
+        <v>7151531</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6328,32 +6281,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113679127</v>
+        <v>113679082</v>
       </c>
       <c r="B55" t="n">
-        <v>79588</v>
+        <v>83358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6363,10 +6316,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457715</v>
+        <v>457694</v>
       </c>
       <c r="R55" t="n">
-        <v>7151534</v>
+        <v>7151641</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6434,32 +6387,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113679130</v>
+        <v>113679083</v>
       </c>
       <c r="B56" t="n">
-        <v>79588</v>
+        <v>83358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6469,10 +6422,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457768</v>
+        <v>457654</v>
       </c>
       <c r="R56" t="n">
-        <v>7151536</v>
+        <v>7151668</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6540,45 +6493,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113680324</v>
+        <v>113679085</v>
       </c>
       <c r="B57" t="n">
-        <v>92876</v>
+        <v>83358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457400</v>
+        <v>457529</v>
       </c>
       <c r="R57" t="n">
-        <v>7151519</v>
+        <v>7151643</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6622,12 +6575,12 @@
       <c r="AG57" t="b">
         <v>0</v>
       </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT57" t="inlineStr"/>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW57" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -6646,45 +6599,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113680340</v>
+        <v>113679086</v>
       </c>
       <c r="B58" t="n">
-        <v>91879</v>
+        <v>83358</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457871</v>
+        <v>457366</v>
       </c>
       <c r="R58" t="n">
-        <v>7151603</v>
+        <v>7151654</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6728,12 +6681,12 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT58" t="inlineStr"/>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW58" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -6752,10 +6705,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113680318</v>
+        <v>113679104</v>
       </c>
       <c r="B59" t="n">
-        <v>91930</v>
+        <v>83358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6763,34 +6716,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457551</v>
+        <v>457453</v>
       </c>
       <c r="R59" t="n">
-        <v>7151637</v>
+        <v>7151510</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6834,12 +6787,12 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT59" t="inlineStr"/>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW59" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -6861,7 +6814,7 @@
         <v>113679107</v>
       </c>
       <c r="B60" t="n">
-        <v>83314</v>
+        <v>83358</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6964,45 +6917,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113679093</v>
+        <v>113679131</v>
       </c>
       <c r="B61" t="n">
-        <v>79588</v>
+        <v>83358</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457385</v>
+        <v>457772</v>
       </c>
       <c r="R61" t="n">
-        <v>7151571</v>
+        <v>7151510</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7070,10 +7023,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113680337</v>
+        <v>113679134</v>
       </c>
       <c r="B62" t="n">
-        <v>83180</v>
+        <v>83358</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7081,21 +7034,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7105,10 +7058,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>457840</v>
+        <v>457913</v>
       </c>
       <c r="R62" t="n">
-        <v>7151527</v>
+        <v>7151566</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7152,12 +7105,12 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW62" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -7176,10 +7129,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113680334</v>
+        <v>113679135</v>
       </c>
       <c r="B63" t="n">
-        <v>91916</v>
+        <v>83358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7187,21 +7140,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7211,10 +7164,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457842</v>
+        <v>457883</v>
       </c>
       <c r="R63" t="n">
-        <v>7151516</v>
+        <v>7151595</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7258,12 +7211,12 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT63" t="inlineStr"/>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW63" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -7282,10 +7235,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113679113</v>
+        <v>113679139</v>
       </c>
       <c r="B64" t="n">
-        <v>80437</v>
+        <v>83358</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7293,21 +7246,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7317,10 +7270,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457606</v>
+        <v>457848</v>
       </c>
       <c r="R64" t="n">
-        <v>7151532</v>
+        <v>7151605</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7388,10 +7341,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113679083</v>
+        <v>113679140</v>
       </c>
       <c r="B65" t="n">
-        <v>83314</v>
+        <v>83358</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7423,10 +7376,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>457654</v>
+        <v>457820</v>
       </c>
       <c r="R65" t="n">
-        <v>7151668</v>
+        <v>7151598</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7494,32 +7447,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113679133</v>
+        <v>113679141</v>
       </c>
       <c r="B66" t="n">
-        <v>80466</v>
+        <v>83358</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7529,10 +7482,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>457815</v>
+        <v>457806</v>
       </c>
       <c r="R66" t="n">
-        <v>7151537</v>
+        <v>7151618</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7600,32 +7553,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113680331</v>
+        <v>105311952</v>
       </c>
       <c r="B67" t="n">
-        <v>91879</v>
+        <v>80432</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7635,13 +7588,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>457728</v>
+        <v>457718</v>
       </c>
       <c r="R67" t="n">
-        <v>7151521</v>
+        <v>7151475</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7665,12 +7618,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7682,12 +7635,17 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
       <c r="AT67" t="inlineStr"/>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW67" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -7695,21 +7653,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113679134</v>
+        <v>110913410</v>
       </c>
       <c r="B68" t="n">
-        <v>83314</v>
+        <v>80432</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7717,37 +7671,38 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>457913</v>
+        <v>457865</v>
       </c>
       <c r="R68" t="n">
-        <v>7151566</v>
+        <v>7151448</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7771,12 +7726,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7787,35 +7742,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113679082</v>
+        <v>113679087</v>
       </c>
       <c r="B69" t="n">
-        <v>83314</v>
+        <v>80488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7823,34 +7769,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>457694</v>
+        <v>457332</v>
       </c>
       <c r="R69" t="n">
-        <v>7151641</v>
+        <v>7151642</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7918,10 +7864,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113679131</v>
+        <v>113679088</v>
       </c>
       <c r="B70" t="n">
-        <v>83314</v>
+        <v>80488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7929,34 +7875,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>457772</v>
+        <v>457335</v>
       </c>
       <c r="R70" t="n">
-        <v>7151510</v>
+        <v>7151600</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8024,45 +7970,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113680335</v>
+        <v>113679096</v>
       </c>
       <c r="B71" t="n">
-        <v>92639</v>
+        <v>80488</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>457831</v>
+        <v>457373</v>
       </c>
       <c r="R71" t="n">
-        <v>7151507</v>
+        <v>7151548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8106,12 +8052,12 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT71" t="inlineStr"/>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW71" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -8130,32 +8076,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113680322</v>
+        <v>113679097</v>
       </c>
       <c r="B72" t="n">
-        <v>91879</v>
+        <v>80488</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8165,10 +8111,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>457373</v>
+        <v>457413</v>
       </c>
       <c r="R72" t="n">
-        <v>7151657</v>
+        <v>7151504</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8212,12 +8158,12 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT72" t="inlineStr"/>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW72" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -8236,10 +8182,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113680338</v>
+        <v>113679099</v>
       </c>
       <c r="B73" t="n">
-        <v>91916</v>
+        <v>80488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8247,34 +8193,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>457864</v>
+        <v>457437</v>
       </c>
       <c r="R73" t="n">
-        <v>7151544</v>
+        <v>7151513</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8318,12 +8264,12 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT73" t="inlineStr"/>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW73" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -8342,10 +8288,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113679106</v>
+        <v>113679113</v>
       </c>
       <c r="B74" t="n">
-        <v>83306</v>
+        <v>80488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8353,21 +8299,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8377,10 +8323,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>457586</v>
+        <v>457606</v>
       </c>
       <c r="R74" t="n">
-        <v>7151563</v>
+        <v>7151532</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8448,10 +8394,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113679129</v>
+        <v>113679124</v>
       </c>
       <c r="B75" t="n">
-        <v>83306</v>
+        <v>80488</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8459,21 +8405,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8483,10 +8429,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>457742</v>
+        <v>457706</v>
       </c>
       <c r="R75" t="n">
-        <v>7151530</v>
+        <v>7151522</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8554,45 +8500,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113680343</v>
+        <v>113679090</v>
       </c>
       <c r="B76" t="n">
-        <v>83180</v>
+        <v>79629</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>6459</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>457803</v>
+        <v>457368</v>
       </c>
       <c r="R76" t="n">
-        <v>7151599</v>
+        <v>7151610</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8636,12 +8582,12 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT76" t="inlineStr"/>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW76" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -8660,45 +8606,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113679122</v>
+        <v>113679093</v>
       </c>
       <c r="B77" t="n">
-        <v>80438</v>
+        <v>79629</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6459</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>457692</v>
+        <v>457385</v>
       </c>
       <c r="R77" t="n">
-        <v>7151526</v>
+        <v>7151571</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8766,10 +8712,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>113679120</v>
+        <v>113679110</v>
       </c>
       <c r="B78" t="n">
-        <v>83297</v>
+        <v>79629</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8777,21 +8723,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6439</v>
+        <v>6459</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8801,10 +8747,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>457679</v>
+        <v>457606</v>
       </c>
       <c r="R78" t="n">
-        <v>7151537</v>
+        <v>7151530</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8872,10 +8818,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113680344</v>
+        <v>113679123</v>
       </c>
       <c r="B79" t="n">
-        <v>91879</v>
+        <v>79629</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8883,21 +8829,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>6459</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8907,10 +8853,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>457785</v>
+        <v>457694</v>
       </c>
       <c r="R79" t="n">
-        <v>7151608</v>
+        <v>7151523</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8954,12 +8900,12 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT79" t="inlineStr"/>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW79" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -8978,10 +8924,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>113679111</v>
+        <v>113679127</v>
       </c>
       <c r="B80" t="n">
-        <v>80466</v>
+        <v>79629</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8989,21 +8935,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9013,10 +8959,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>457607</v>
+        <v>457715</v>
       </c>
       <c r="R80" t="n">
-        <v>7151536</v>
+        <v>7151534</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9084,32 +9030,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113680327</v>
+        <v>113679130</v>
       </c>
       <c r="B81" t="n">
-        <v>91916</v>
+        <v>79629</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9119,10 +9065,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>457538</v>
+        <v>457768</v>
       </c>
       <c r="R81" t="n">
-        <v>7151581</v>
+        <v>7151536</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9166,12 +9112,12 @@
       <c r="AG81" t="b">
         <v>0</v>
       </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT81" t="inlineStr"/>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW81" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -9190,45 +9136,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>113679137</v>
+        <v>113679092</v>
       </c>
       <c r="B82" t="n">
-        <v>79491</v>
+        <v>80493</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1249</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>457878</v>
+        <v>457382</v>
       </c>
       <c r="R82" t="n">
-        <v>7151593</v>
+        <v>7151577</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9296,45 +9242,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>113680346</v>
+        <v>113679102</v>
       </c>
       <c r="B83" t="n">
-        <v>83180</v>
+        <v>80493</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>457802</v>
+        <v>457437</v>
       </c>
       <c r="R83" t="n">
-        <v>7151613</v>
+        <v>7151514</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9378,12 +9324,12 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT83" t="inlineStr"/>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW83" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -9402,32 +9348,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113679141</v>
+        <v>113679111</v>
       </c>
       <c r="B84" t="n">
-        <v>83314</v>
+        <v>80493</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9437,10 +9383,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>457806</v>
+        <v>457607</v>
       </c>
       <c r="R84" t="n">
-        <v>7151618</v>
+        <v>7151536</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9508,10 +9454,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>113679090</v>
+        <v>113679117</v>
       </c>
       <c r="B85" t="n">
-        <v>79588</v>
+        <v>80493</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9519,34 +9465,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6459</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>457368</v>
+        <v>457678</v>
       </c>
       <c r="R85" t="n">
-        <v>7151610</v>
+        <v>7151491</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9614,10 +9560,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113678017</v>
+        <v>113679133</v>
       </c>
       <c r="B86" t="n">
-        <v>96345</v>
+        <v>80493</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9625,38 +9571,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>457707</v>
+        <v>457815</v>
       </c>
       <c r="R86" t="n">
-        <v>7151539</v>
+        <v>7151537</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9697,9 +9639,13 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9720,10 +9666,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>113678016</v>
+        <v>113679094</v>
       </c>
       <c r="B87" t="n">
-        <v>96345</v>
+        <v>80499</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9731,38 +9677,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2809</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>457465</v>
+        <v>457381</v>
       </c>
       <c r="R87" t="n">
-        <v>7151542</v>
+        <v>7151579</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9803,9 +9745,13 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -9826,49 +9772,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>113678015</v>
+        <v>113679116</v>
       </c>
       <c r="B88" t="n">
-        <v>97365</v>
+        <v>80499</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>457373</v>
+        <v>457677</v>
       </c>
       <c r="R88" t="n">
-        <v>7151572</v>
+        <v>7151501</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9909,9 +9851,13 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -9932,49 +9878,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>113678019</v>
+        <v>113679118</v>
       </c>
       <c r="B89" t="n">
-        <v>97365</v>
+        <v>80499</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>6463</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>457730</v>
+        <v>457687</v>
       </c>
       <c r="R89" t="n">
-        <v>7151536</v>
+        <v>7151509</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10015,9 +9957,13 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -10038,10 +9984,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>113678021</v>
+        <v>105311953</v>
       </c>
       <c r="B90" t="n">
-        <v>96345</v>
+        <v>80468</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10049,41 +9995,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>457872</v>
+        <v>457740</v>
       </c>
       <c r="R90" t="n">
-        <v>7151605</v>
+        <v>7151460</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10107,12 +10049,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10121,9 +10063,13 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10133,60 +10079,52 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>113678020</v>
+        <v>113679103</v>
       </c>
       <c r="B91" t="n">
-        <v>97365</v>
+        <v>80500</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>53</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Framnäs, Jmt</t>
+          <t>Flygfält, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>457743</v>
+        <v>457439</v>
       </c>
       <c r="R91" t="n">
-        <v>7151536</v>
+        <v>7151514</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10227,9 +10165,13 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -10250,10 +10192,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>113678018</v>
+        <v>113679126</v>
       </c>
       <c r="B92" t="n">
-        <v>96357</v>
+        <v>80500</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10261,38 +10203,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2813</v>
+        <v>6464</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>457732</v>
+        <v>457698</v>
       </c>
       <c r="R92" t="n">
-        <v>7151541</v>
+        <v>7151521</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10333,9 +10271,13 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10356,10 +10298,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>113678014</v>
+        <v>113679132</v>
       </c>
       <c r="B93" t="n">
-        <v>96345</v>
+        <v>80500</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10367,38 +10309,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Flygfält, Jmt</t>
+          <t>Framnäs, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>457372</v>
+        <v>457805</v>
       </c>
       <c r="R93" t="n">
-        <v>7151602</v>
+        <v>7151514</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10439,9 +10377,13 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -10455,6 +10397,324 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>113682611</v>
+      </c>
+      <c r="B94" t="n">
+        <v>108274</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Flygfält, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>457466</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7151567</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>113682612</v>
+      </c>
+      <c r="B95" t="n">
+        <v>108274</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Framnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>457585</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7151534</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>113679098</v>
+      </c>
+      <c r="B96" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Flygfält, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>457435</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7151509</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 29945-2022 artfynd.xlsx
+++ b/artfynd/A 29945-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678015</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678019</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678020</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680333</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679106</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679121</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679129</t>
         </is>
       </c>
     </row>
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111011864</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680328</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680336</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315253</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1935,6 +1995,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680327</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,6 +2106,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680329</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,6 +2217,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680334</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680338</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2359,6 +2439,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680318</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680339</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2573,6 +2663,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112328247</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2679,6 +2774,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679137</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2785,6 +2885,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680319</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2891,6 +2996,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680321</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2997,6 +3107,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680330</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3103,6 +3218,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680337</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3209,6 +3329,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680342</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3315,6 +3440,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680343</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3421,6 +3551,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680346</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3525,6 +3660,11 @@
       <c r="AY28" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679084</t>
         </is>
       </c>
     </row>
@@ -3628,6 +3768,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111011899</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3734,6 +3879,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679091</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3840,6 +3990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679095</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3946,6 +4101,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679100</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4052,6 +4212,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679108</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4158,6 +4323,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679119</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4262,6 +4432,11 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679122</t>
         </is>
       </c>
     </row>
@@ -4370,6 +4545,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678014</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4476,6 +4656,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678016</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4582,6 +4767,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678017</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4688,6 +4878,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678021</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4794,6 +4989,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678018</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4900,6 +5100,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680335</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5006,6 +5211,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680324</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5112,6 +5322,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680317</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5218,6 +5433,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680322</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5324,6 +5544,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680325</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5430,6 +5655,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680326</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5536,6 +5766,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680331</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5642,6 +5877,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680340</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5748,6 +5988,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680341</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5854,6 +6099,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680344</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5960,6 +6210,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680345</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6066,6 +6321,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679142</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6172,6 +6432,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679120</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6278,6 +6543,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679128</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6384,6 +6654,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679082</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6490,6 +6765,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679083</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6596,6 +6876,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679085</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6702,6 +6987,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679086</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6808,6 +7098,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679104</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6914,6 +7209,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679107</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7020,6 +7320,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679131</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7126,6 +7431,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679134</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7232,6 +7542,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679135</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7338,6 +7653,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679139</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7444,6 +7764,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679140</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7550,6 +7875,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679141</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7657,6 +7987,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311952</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7755,6 +8090,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110913410</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7861,6 +8201,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679087</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7967,6 +8312,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679088</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8073,6 +8423,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679096</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8179,6 +8534,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679097</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8285,6 +8645,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679099</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8391,6 +8756,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679113</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8497,6 +8867,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679124</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8603,6 +8978,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679090</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8709,6 +9089,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679093</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8815,6 +9200,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679110</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8921,6 +9311,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679123</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9027,6 +9422,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679127</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9133,6 +9533,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679130</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9239,6 +9644,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679092</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9345,6 +9755,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679102</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9451,6 +9866,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679111</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9557,6 +9977,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679117</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9663,6 +10088,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679133</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9769,6 +10199,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679094</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9875,6 +10310,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679116</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9981,6 +10421,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679118</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10083,6 +10528,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311953</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10189,6 +10639,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679103</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10295,6 +10750,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679126</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10401,6 +10861,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679132</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10507,6 +10972,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113682611</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10613,6 +11083,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113682612</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10719,8 +11194,110 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679098</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>